--- a/uploads/data.xlsx
+++ b/uploads/data.xlsx
@@ -527,7 +527,7 @@
         <v>94</v>
       </c>
       <c r="H3" t="n">
-        <v>6.153846153846154</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>64</v>
       </c>
       <c r="H5" t="n">
-        <v>8.384615384615385</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -617,7 +617,7 @@
         <v>95</v>
       </c>
       <c r="H6" t="n">
-        <v>6.153846153846154</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>82</v>
       </c>
       <c r="H7" t="n">
-        <v>8.923076923076923</v>
+        <v>8.92</v>
       </c>
     </row>
   </sheetData>
